--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Microsoft Power BI Technical Specialist</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4eb0dda56977ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=102b1b66407c2d63</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102b1b66407c2d63</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec018f4b793bb53</t>
         </is>
       </c>
     </row>
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec018f4b793bb53</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5406e0a898c0b3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5406e0a898c0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=51afe960d8622afb</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51afe960d8622afb</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bdbda24615b096</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bdbda24615b096</t>
+          <t>https://www.indeed.com/viewjob?jk=8a792597231fd045</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a792597231fd045</t>
+          <t>https://www.indeed.com/viewjob?jk=49b79f56ab220c49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>FalconSmartIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b79f56ab220c49</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c0d190ff6325ff</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41ec093c0ab2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Azure Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FalconSmartIT</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c0d190ff6325ff</t>
+          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf4c231be457587</t>
+          <t>https://www.indeed.com/viewjob?jk=f63d74803f449e20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f22e872cda096bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, DBT, ETL)</t>
+          <t>Senior Decision Intelligence Engineer (NBA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1c4c6a8a8c46e</t>
+          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, DBT, ETL)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e11531ce39be3674</t>
+          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, DBT, ETL)</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82f7de5f84e4fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Databricks Data Engineer</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Full-Stack Developer - Integrations</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
+          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Site Reliability Engineer (SRE) with Data Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Integrations</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
+          <t>https://www.indeed.com/viewjob?jk=5104197d6abcdbd0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5680d993aab0f3e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) with Data Platform</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
+          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5104197d6abcdbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5680d993aab0f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>DevOps Engineer - Westlake, TX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>DevOps Engineer - Jersey City, NJ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>DevOps Engineer - Merrimack, NH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>Sr. Analyst, Data Modeling</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
+          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
+          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7916ae467b0427c</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow - East Coast</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Multi Cloud</t>
+          <t>Senior Solutions Architect - Airflow - East Coast</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
+          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer III - REMOTE</t>
+          <t>Enterprise Architect - Multi Cloud</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
+          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>DevOps Engineer III - REMOTE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
+          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d0311822cd0b6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=cc47198a456f1266</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
         </is>
       </c>
     </row>
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Intelligence Analyst</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f523df076b59e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Engineer</t>
+          <t>Data Intelligence Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=1f523df076b59e1d</t>
         </is>
       </c>
     </row>
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acacc051b98d38c6</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Software Engineer III - AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f024c7e74dd527d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b93d7ce229e42e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6707e3755a595393</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>Data Engineer L2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Cloud Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31872c8b26f562e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Generative AI / Enterprise Data Senior Architect</t>
+          <t>Senior AWS Cloud Engineer- VDI Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Dynamics Land Systems</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
+          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd2826582327ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6468a261c686526f</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Senior Solutions Architect, Media and Broadcasting</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, Azure, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
+          <t>https://www.indeed.com/viewjob?jk=a03574605c9e38ea</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38048ba50b2a7b19</t>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sporttrade</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
+          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3279830533b369e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f2b62d5373727f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ca139b5ce94a22</t>
+          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior IT Systems Engineer-ORCA</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sound Transit</t>
+          <t>Sporttrade</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI Natives Business, Strategic</t>
+          <t>Healthcare Data Scientist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ea35aceaecf2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+          <t>Senior IT Systems Engineer-ORCA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sound Transit</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
+          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
+          <t>Sr. Backend Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d04b632592cdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Data Applications Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,42 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>FalconSmartIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec018f4b793bb53</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c0d190ff6325ff</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5406e0a898c0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a76e43ef1f5bbfd7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51afe960d8622afb</t>
+          <t>https://www.indeed.com/viewjob?jk=24a167e7c74c87d9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bdbda24615b096</t>
+          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a792597231fd045</t>
+          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.5</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b79f56ab220c49</t>
+          <t>https://www.indeed.com/viewjob?jk=f63d74803f449e20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FalconSmartIT</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c0d190ff6325ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Decision Intelligence Engineer (NBA)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Databricks Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f63d74803f449e20</t>
+          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Full-Stack Developer - Integrations</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
+          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Site Reliability Engineer (SRE) with Data Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Integrations</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
+          <t>https://www.indeed.com/viewjob?jk=d5680d993aab0f3e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) with Data Platform</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
+          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
+          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer III (Java/Microservices/AWS)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5104197d6abcdbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>DevOps Engineer - Westlake, TX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5680d993aab0f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>DevOps Engineer - Jersey City, NJ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>DevOps Engineer - Merrimack, NH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Sr. Analyst, Data Modeling</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
+          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
+          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Senior Solutions Architect - Airflow - East Coast</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Enterprise Architect - Multi Cloud</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>DevOps Engineer III - REMOTE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow - East Coast</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
+          <t>https://www.indeed.com/viewjob?jk=cc47198a456f1266</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Multi Cloud</t>
+          <t>Sr. Power BI Developer &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cornerstone Advisors</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer III - REMOTE</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
+          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Software Engineer - Core Automation Platform</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc47198a456f1266</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
+          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
         </is>
       </c>
     </row>
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Data Intelligence Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=1f523df076b59e1d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Intelligence Analyst</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f523df076b59e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer II - SaaS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Engineer</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer L2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer L2</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>Cloud Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Senior AWS Cloud Engineer- VDI Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer- VDI Platform</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Generative AI / Enterprise Data Senior Architect</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>General Dynamics Land Systems</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Automation Tester</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Solutions Architect, Media and Broadcasting</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, Azure, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
+          <t>https://www.indeed.com/viewjob?jk=a03574605c9e38ea</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect, Media and Broadcasting</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, Azure, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03574605c9e38ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
+          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PurpleLab</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sporttrade</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
+          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist</t>
+          <t>Senior Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior IT Systems Engineer-ORCA</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sound Transit</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
+          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Sporttrade</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Applications Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Scientist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Security Automation Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d30468ca7ed7236</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior IT Systems Engineer-ORCA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Sound Transit</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,19 +4031,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+          <t>Data Applications Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,15 +4091,225 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Engineer Java · Spring Boot · Connected Services</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Kimball Midwest</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
         </is>

--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a167e7c74c87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Databricks Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
+          <t>https://www.indeed.com/viewjob?jk=f63d74803f449e20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f63d74803f449e20</t>
+          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Decision Intelligence Engineer (NBA)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
+          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
+          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Full-Stack Developer - Integrations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
+          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Integrations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer (SRE) with Data Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) with Data Platform</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Software Engineer III (Java/Microservices/AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
+          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5680d993aab0f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
+          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
+          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>DevOps Engineer - Westlake, TX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Microservices/AWS)</t>
+          <t>DevOps Engineer - Jersey City, NJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>DevOps Engineer - Merrimack, NH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>Clinic System Administrator</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University of the Pacific</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>Senior Analyst, Data Modeling</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
+          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
+          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
+          <t>Enterprise Architect - Multi Cloud</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow - East Coast</t>
+          <t>DevOps Engineer III - REMOTE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
+          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Multi Cloud</t>
+          <t>Senior Solutions Architect - Airflow - East Coast</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
+          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer III - REMOTE</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
+          <t>https://www.indeed.com/viewjob?jk=cc47198a456f1266</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Power BI Developer &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Cornerstone Advisors</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc47198a456f1266</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Power BI Developer &amp; Data Analyst</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cornerstone Advisors</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
+          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Sr. Software Engineer - Core Automation Platform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Intelligence Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f523df076b59e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer II - SaaS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
         </is>
       </c>
     </row>
@@ -2393,25 +2393,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>Perception Validation Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>PlusAI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f695b1026950547b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Cloud Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
+          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer- VDI Platform</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior AWS Cloud Engineer- VDI Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
+          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Generative AI / Enterprise Data Senior Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Dynamics Land Systems</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Automation Tester</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect, Media and Broadcasting</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, Azure, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03574605c9e38ea</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Senior Solutions Architect, Media and Broadcasting</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, Azure, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
+          <t>https://www.indeed.com/viewjob?jk=a03574605c9e38ea</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
+          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PurpleLab</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sporttrade</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
+          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist</t>
+          <t>Senior Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Security Automation Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d30468ca7ed7236</t>
+          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior IT Systems Engineer-ORCA</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sound Transit</t>
+          <t>Sporttrade</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Applications Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Scientist</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Security Automation Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9d30468ca7ed7236</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer Java · Spring Boot · Connected Services</t>
+          <t>Data Applications Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
+          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Backend Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+          <t>Senior IT Systems Engineer-ORCA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sound Transit</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,15 +4301,190 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Software Engineer Java · Spring Boot · Connected Services</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Kimball Midwest</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
         </is>

--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
+          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) with Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Site Reliability Engineer (SRE) with Data Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Microservices/AWS)</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Software Engineer III (Java/Microservices/AWS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
+          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
+          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>DevOps Engineer - Westlake, TX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>DevOps Engineer - Jersey City, NJ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clinic System Administrator</t>
+          <t>DevOps Engineer - Merrimack, NH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>University of the Pacific</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Modeling</t>
+          <t>Clinic System Administrator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>University of the Pacific</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analyst, Data Modeling</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
+          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
@@ -1833,25 +1833,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Power BI Developer &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Cornerstone Advisors</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc47198a456f1266</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Power BI Developer &amp; Data Analyst</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cornerstone Advisors</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
+          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
+          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Sr. Software Engineer - Core Automation Platform</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer II - SaaS</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
         </is>
       </c>
     </row>
@@ -2206,29 +2206,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Data Engineer L2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
+          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer L2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Perception Validation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>PlusAI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=f695b1026950547b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Perception Validation Engineer</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlusAI</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f695b1026950547b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Senior AWS Cloud Engineer- VDI Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer- VDI Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Generative AI / Enterprise Data Senior Architect</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Dynamics Land Systems</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Automation Tester</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
+          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
+          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
+          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
         </is>
       </c>
     </row>
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
+          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
         </is>
       </c>
     </row>
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
+          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>PurpleLab</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
+          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>Senior Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sporttrade</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sporttrade</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Healthcare Data Scientist</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist</t>
+          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Applications Engineer</t>
+          <t>Backend Software Engineer Graduate (TikTok-PGC-Digital Content Center) - 2027 Start</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d22af308ad0bf59</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Applications Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior IT Systems Engineer-ORCA</t>
+          <t>Sr. Backend Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sound Transit</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior IT Systems Engineer-ORCA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Sound Transit</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer Java · Spring Boot · Connected Services</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
+          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Software Engineer Java · Spring Boot · Connected Services</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4485,6 +4485,41 @@
         </is>
       </c>
       <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
         </is>

--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -561,12 +561,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76e43ef1f5bbfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
         </is>
       </c>
     </row>
@@ -578,20 +578,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=a76e43ef1f5bbfd7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
+          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Azure Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f63d74803f449e20</t>
+          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
+          <t>https://www.indeed.com/viewjob?jk=f63d74803f449e20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
+          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Decision Intelligence Engineer (NBA)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
+          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Senior Software Engineer - AI Agentic Product Dev</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e86e219dc8ab5e9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Sr. Software Engineer - Core Automation Platform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer II - SaaS</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
@@ -2206,29 +2206,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer L2</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer L2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Perception Validation Engineer</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PlusAI</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f695b1026950547b</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Perception Validation Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>PlusAI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=f695b1026950547b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Cloud Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer- VDI Platform</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior AWS Cloud Engineer- VDI Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
+          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Generative AI / Enterprise Data Senior Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Dynamics Land Systems</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,59 +3016,59 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Automation Tester</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect, Media and Broadcasting</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, Azure, CI/CD, Terraform, Docker</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03574605c9e38ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
+          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Senior Solutions Architect, Media and Broadcasting</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, Azure, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a03574605c9e38ea</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
+          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
         </is>
       </c>
     </row>
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
+          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>PurpleLab</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sporttrade</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Sporttrade</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Security Automation Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d30468ca7ed7236</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Backend Software Engineer Graduate (TikTok-PGC-Digital Content Center) - 2027 Start</t>
+          <t>Healthcare Data Scientist</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d22af308ad0bf59</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Applications Engineer</t>
+          <t>Security Automation Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d30468ca7ed7236</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Software Engineer Graduate (TikTok-PGC-Digital Content Center) - 2027 Start</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+          <t>https://www.indeed.com/viewjob?jk=4d22af308ad0bf59</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior IT Systems Engineer-ORCA</t>
+          <t>Data Applications Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sound Transit</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
+          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer Java · Spring Boot · Connected Services</t>
+          <t>Sr. Backend Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior IT Systems Engineer-ORCA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sound Transit</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+          <t>Software Engineer Java · Spring Boot · Connected Services</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,15 +4511,155 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Kimball Midwest</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f657fa9f2d4f746</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
         </is>

--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,52 +678,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f63d74803f449e20</t>
+          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Decision Intelligence Engineer (NBA)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
+          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-Stack Developer - Integrations</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
+          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Integrations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III (Java/Microservices/AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
+          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) with Data Platform</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
+          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
+          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Microservices/AWS)</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
+          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>DevOps Engineer - Westlake, TX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>DevOps Engineer - Jersey City, NJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>DevOps Engineer - Merrimack, NH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>Clinic System Administrator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University of the Pacific</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>Senior Analyst, Data Modeling</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clinic System Administrator</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>University of the Pacific</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
+          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
+          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
+          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>DevOps Engineer III - REMOTE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Enterprise Architect - Multi Cloud</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
+          <t>Senior Solutions Architect - Airflow - East Coast</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Multi Cloud</t>
+          <t>Sr. Power BI Developer &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cornerstone Advisors</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer III - REMOTE</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
+          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow - East Coast</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
+          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Power BI Developer &amp; Data Analyst</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cornerstone Advisors</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
+          <t>https://www.indeed.com/viewjob?jk=649769363a6c45f2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Agentic Product Dev</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e86e219dc8ab5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Sr. Software Engineer - Core Automation Platform</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer II - SaaS</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
         </is>
       </c>
     </row>
@@ -2206,29 +2206,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Data Engineer L2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
+          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer L2</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>Perception Validation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>PlusAI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=f695b1026950547b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Perception Validation Engineer</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlusAI</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f695b1026950547b</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>MedaSync LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Cloud Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Senior AWS Cloud Engineer- VDI Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer- VDI Platform</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Generative AI / Enterprise Data Senior Architect</t>
+          <t>Automation Tester</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Dynamics Land Systems</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,102 +2946,102 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d3ae94d02ca0b5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Kronos Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec014fc719d00ce6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
+          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
+          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
         </is>
       </c>
     </row>
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
+          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>PurpleLab</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>Senior Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Sporttrade</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Healthcare Data Scientist</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sporttrade</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist</t>
+          <t>Security Automation Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d30468ca7ed7236</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Security Automation Engineer</t>
+          <t>Backend Software Engineer Graduate (TikTok-PGC-Digital Content Center) - 2027 Start</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d30468ca7ed7236</t>
+          <t>https://www.indeed.com/viewjob?jk=4d22af308ad0bf59</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Backend Software Engineer Graduate (TikTok-PGC-Digital Content Center) - 2027 Start</t>
+          <t>Software Engineer Java · Spring Boot · Connected Services</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d22af308ad0bf59</t>
+          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Applications Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f657fa9f2d4f746</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Data Applications Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer Java · Spring Boot · Connected Services</t>
+          <t>Sr. Backend Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4555,111 +4555,6 @@
         </is>
       </c>
       <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f657fa9f2d4f746</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
         </is>

--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Databricks Data Engineer</t>
+          <t>Technical Solutions Architect II -- Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
+          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
+          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Data Engineer Dremio</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
+          <t>https://www.indeed.com/viewjob?jk=aab2a218af47694f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Integrations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
+          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
+          <t>Senior Decision Intelligence Engineer (NBA)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Full-Stack Developer - Integrations</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
+          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Microservices/AWS)</t>
+          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
+          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Software Engineer III (Java/Microservices/AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
+          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
+          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>Clinic System Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University of the Pacific</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Clinic System Administrator</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>University of the Pacific</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e96a2863adf9faa0</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>VASERJOB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb076d58305c59a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Enterprise Architect - Multi Cloud</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Multi Cloud</t>
+          <t>Senior Solutions Architect - Airflow - East Coast</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,42 +1686,42 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
+          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow - East Coast</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
+          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649769363a6c45f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer II - SaaS</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Branson, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
+          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Elizabethtown, KY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
+          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Sr. Software Engineer - Core Automation Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer L2</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Perception Validation Engineer</t>
+          <t>Data Engineer L2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PlusAI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f695b1026950547b</t>
+          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,59 +2456,59 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MedaSync LLC</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MedaSync LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Cloud Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer- VDI Platform</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior AWS Cloud Engineer- VDI Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
+          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
+          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Generative AI / Enterprise Data Senior Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>General Dynamics Land Systems</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Automation Tester</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,94 +2946,94 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d3ae94d02ca0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kronos Consultant</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec014fc719d00ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7139ab3ddc5daefd</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect, Media and Broadcasting</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, Azure, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03574605c9e38ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c354f6d93d13200a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d3ae94d02ca0b5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Kronos Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec014fc719d00ce6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
+          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
+          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Electric Hydrogen</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd11edfa704b3c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
+          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>PurpleLab</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sporttrade</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Sporttrade</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Security Automation Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d30468ca7ed7236</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Backend Software Engineer Graduate (TikTok-PGC-Digital Content Center) - 2027 Start</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d22af308ad0bf59</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffdcc3ef0b5287</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer Java · Spring Boot · Connected Services</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
+          <t>https://www.indeed.com/viewjob?jk=2585369e0ced4f85</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Now100 Inc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+          <t>https://www.indeed.com/viewjob?jk=481c0948c82cd1a4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+          <t>PLM Technical Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f657fa9f2d4f746</t>
+          <t>https://www.indeed.com/viewjob?jk=7bf176d2c7022fbc</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior IT Systems Engineer-ORCA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sound Transit</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Software Engineer Java · Spring Boot · Connected Services</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Technical Architect - Platform - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FalconSmartIT</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c0d190ff6325ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d56ba0f8432c551e</t>
         </is>
       </c>
     </row>
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
+          <t>https://www.indeed.com/viewjob?jk=f63d74803f449e20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer Dremio</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aab2a218af47694f</t>
+          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Dremio</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
+          <t>https://www.indeed.com/viewjob?jk=aab2a218af47694f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
+          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Senior Decision Intelligence Engineer (NBA)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
+          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Integrations</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,54 +916,54 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
+          <t>Full-Stack Developer - Integrations</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
+          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Microservices/AWS)</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Sr Java Backend (Miami Lakes)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4db5adddb13236</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Software Engineer III (Java/Microservices/AWS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
+          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Clinic System Administrator</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>University of the Pacific</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96a2863adf9faa0</t>
+          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Modeling</t>
+          <t>Senior Software Engineer Java</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
+          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Clinic System Administrator</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>University of the Pacific</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e96a2863adf9faa0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
+          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Solutions Architect - Airflow - East Coast</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VASERJOB</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb076d58305c59a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Multi Cloud</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VASERJOB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb076d58305c59a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer III - REMOTE</t>
+          <t>Sr. Power BI Developer &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Cornerstone Advisors</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow - East Coast</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
+          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Power BI Developer &amp; Data Analyst</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cornerstone Advisors</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Branson, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
+          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Elizabethtown, KY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
+          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
+          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Branson, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Elizabethtown, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer II - SaaS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,112 +2061,112 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Soho Square Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
+          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Data Engineer L2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>MedaSync LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb8660c0e5ef8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Cloud Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5549d0abdaa34a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer L2</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,129 +2386,129 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Senior AWS Cloud Engineer- VDI Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>LLM Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>iTemp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=e165dc93aab1e2b5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MedaSync LLC</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Automation Tester</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer- VDI Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,199 +2841,199 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Systems Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Taylor, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
+          <t>https://www.indeed.com/viewjob?jk=fa009f1d9ad37c54</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Generative AI / Enterprise Data Senior Architect</t>
+          <t>Senior Security Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>General Dynamics Land Systems</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
+          <t>https://www.indeed.com/viewjob?jk=b20b04f614c47a99</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Electric Hydrogen</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd11edfa704b3c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=c354f6d93d13200a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
+          <t>https://www.indeed.com/viewjob?jk=7139ab3ddc5daefd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d3ae94d02ca0b5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kronos Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec014fc719d00ce6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Software Developer, Applications</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>O'Fallon, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>ECS, RDS, Scala, Jenkins, Maven, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=615774aaccc3425f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
+          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7139ab3ddc5daefd</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c354f6d93d13200a</t>
+          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d3ae94d02ca0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Kronos Consultant</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec014fc719d00ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate Security Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
+          <t>https://www.indeed.com/viewjob?jk=6a21fa934a55c949</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Electric Hydrogen</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,137 +3681,137 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd11edfa704b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PurpleLab</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
+          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,59 +3856,59 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sporttrade</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sporttrade</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffdcc3ef0b5287</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Now100 Inc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,29 +4161,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=481c0948c82cd1a4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffdcc3ef0b5287</t>
+          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Data Applications Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2585369e0ced4f85</t>
+          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Now100 Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481c0948c82cd1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
+          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PLM Technical Consultant</t>
+          <t>Software Engineer Java · Spring Boot · Connected Services</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bf176d2c7022fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Applications Engineer</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,157 +4406,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Everforth ECS</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Software Engineer Java · Spring Boot · Connected Services</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,87 +608,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Reporting &amp; Analytics Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technical Solutions Architect II -- Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
+          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Databricks Data Engineer</t>
+          <t>Technical Solutions Architect II -- Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Aries Computer Systems, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
+          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Integrations</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
+          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
+          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Java Backend (Miami Lakes)</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4db5adddb13236</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
+          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Temporary - Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow - East Coast</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VASERJOB</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb076d58305c59a</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
+          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Power BI Developer &amp; Data Analyst</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cornerstone Advisors</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
+          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>McNees Wallace &amp; Nurick</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Power BI Developer &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Cornerstone Advisors</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
+          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Branson, MO, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Elizabethtown, KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer II - SaaS</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Branson, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Elizabethtown, KY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,112 +2061,112 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
+          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Practicing Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Soho Square Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer L2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
+          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Soho Square Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MedaSync LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
+          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=54759aa3ffee8233</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Data Engineer L2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
+          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer- VDI Platform</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MedaSync LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
+          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Senior AWS Cloud Engineer- VDI Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
+          <t>https://www.indeed.com/viewjob?jk=69fcdae371e385d5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LLM Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>iTemp</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e165dc93aab1e2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
+          <t>https://www.indeed.com/viewjob?jk=35f46c60eb5eb938</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
+          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Automation Tester</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Systems Reliability Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa009f1d9ad37c54</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Security Software Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20b04f614c47a99</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Electric Hydrogen</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd11edfa704b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c354f6d93d13200a</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7139ab3ddc5daefd</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>Senior Systems Reliability Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Taylor, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d3ae94d02ca0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa009f1d9ad37c54</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kronos Consultant</t>
+          <t>Senior Security Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec014fc719d00ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=b20b04f614c47a99</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
+          <t>https://www.indeed.com/viewjob?jk=7139ab3ddc5daefd</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d54dedf311b8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf32d525242f01a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0f129d3d540261</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Associate Security Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,112 +3461,112 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cae2fa18178656</t>
+          <t>https://www.indeed.com/viewjob?jk=6a21fa934a55c949</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate Security Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a21fa934a55c949</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>PurpleLab</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>VulcanForms Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Devens, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
+          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sporttrade</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Mid/Senior Full Stack Java Developer (w/ experience in UI/UX and Angular Testing Frameworks_</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Kaizen Solutions Group</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf534b4f57bf0b99</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffdcc3ef0b5287</t>
+          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Now100 Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481c0948c82cd1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffdcc3ef0b5287</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Enterprise Finance/Operational)</t>
+          <t>Data Applications Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd29dc89ebed116e</t>
+          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Applications Engineer</t>
+          <t>Software Developer / AI Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>PARKWOOD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
+          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Java · Spring Boot · Connected Services</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer Java · Spring Boot · Connected Services</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
+          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full stack Developer (Java - React JS)</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>Senior Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,42 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc0e618cf1de443</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Med-Metrix</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=224f644ff51634b1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-04.xlsx
+++ b/results/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Technical Architect - Platform - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,46 +482,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102b1b66407c2d63</t>
+          <t>https://www.indeed.com/viewjob?jk=d56ba0f8432c551e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Technical Architect - Platform - Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56ba0f8432c551e</t>
+          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -561,29 +561,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a76e43ef1f5bbfd7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76e43ef1f5bbfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer Dremio</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Aries Computer Systems, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aab2a218af47694f</t>
+          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
+          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
+          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aries Computer Systems, Inc.</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
+          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
@@ -963,20 +963,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
+          <t>Software Engineer III (Java/Microservices/AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Clinic System Administrator</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>University of the Pacific</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
+          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Microservices/AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,172 +1126,172 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
+          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
+          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
+          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clinic System Administrator</t>
+          <t>Temporary - Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>University of the Pacific</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96a2863adf9faa0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Temporary - Data Engineer</t>
+          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
+          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Rush University Medical Center</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
+          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Data Platform &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>McNees Wallace &amp; Nurick</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Power BI Developer &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>Cornerstone Advisors</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Integration Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>McNees Wallace &amp; Nurick</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
+          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
+          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Power BI Developer &amp; Data Analyst</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cornerstone Advisors</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Branson, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
+          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Elizabethtown, KY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
+          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
+          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Owl Labs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Branson, MO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7383687e3e9016</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Owl Labs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Elizabethtown, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a71d06adc0eea81c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Owl Labs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0230aad2426cbb0e</t>
         </is>
       </c>
     </row>
@@ -2043,95 +2043,95 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=d703a95f6d98132d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
+          <t>https://www.indeed.com/viewjob?jk=43612f69ee01f601</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Soho Square Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=54759aa3ffee8233</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Soho Square Solutions</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer L2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,94 +2351,94 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54759aa3ffee8233</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a49d7ee8cbacdd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer L2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29005ad10a028330</t>
+          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
+          <t>https://www.indeed.com/viewjob?jk=35f46c60eb5eb938</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f46c60eb5eb938</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
+          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Senior Data Warehouse Administrator</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
+          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,77 +2831,77 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Automation Tester</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Site Reliability Engineer - Workflow Automation</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,29 +3076,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Systems Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa009f1d9ad37c54</t>
+          <t>https://www.indeed.com/viewjob?jk=a8be518fe482570d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Security Software Engineer</t>
+          <t>Solution Architect - Senior</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20b04f614c47a99</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b20c7e930af523</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Senior Systems Reliability Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Taylor, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7139ab3ddc5daefd</t>
+          <t>https://www.indeed.com/viewjob?jk=fa009f1d9ad37c54</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior Software Developer, Applications</t>
+          <t>Senior Security Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>O'Fallon, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ECS, RDS, Scala, Jenkins, Maven, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615774aaccc3425f</t>
+          <t>https://www.indeed.com/viewjob?jk=b20b04f614c47a99</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7139ab3ddc5daefd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Junior Software Developer, Applications</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>O'Fallon, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>ECS, RDS, Scala, Jenkins, Maven, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=615774aaccc3425f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
+          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Security Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a21fa934a55c949</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Wizards)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VulcanForms Inc.</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Devens, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>PurpleLab</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>VulcanForms Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Devens, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Integrations Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,19 +4031,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT, MLOps, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bcd8bc3a260293</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mid/Senior Full Stack Java Developer (w/ experience in UI/UX and Angular Testing Frameworks_</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kaizen Solutions Group</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf534b4f57bf0b99</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Mid/Senior Full Stack Java Developer (w/ experience in UI/UX and Angular Testing Frameworks_</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kaizen Solutions Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffdcc3ef0b5287</t>
+          <t>https://www.indeed.com/viewjob?jk=cf534b4f57bf0b99</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Applications Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, Scala, Data Modeling, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5734efca71e9437a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Developer / AI Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PARKWOOD</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffdcc3ef0b5287</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer Java · Spring Boot · Connected Services</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Full stack Developer (Java - React JS)</t>
+          <t>Software Developer / AI Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PARKWOOD</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer Java · Spring Boot · Connected Services</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud Engineer</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc0e618cf1de443</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud Engineer</t>
+          <t>QA Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>Sustainment</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,15 +4441,155 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sr. Data Analytics Developer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>StandardAero</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Med-Metrix</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fc0e618cf1de443</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Med-Metrix</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=224f644ff51634b1</t>
         </is>
